--- a/dashboard/assets/notas/especial-2025.xlsx
+++ b/dashboard/assets/notas/especial-2025.xlsx
@@ -1,385 +1,44 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <Application>Microsoft Excel</Application>
-  <DocSecurity>0</DocSecurity>
-  <ScaleCrop>false</ScaleCrop>
-  <HeadingPairs>
-    <vt:vector size="2" baseType="variant">
-      <vt:variant>
-        <vt:lpstr>Planilhas</vt:lpstr>
-      </vt:variant>
-      <vt:variant>
-        <vt:i4>7</vt:i4>
-      </vt:variant>
-    </vt:vector>
-  </HeadingPairs>
-  <TitlesOfParts>
-    <vt:vector size="7" baseType="lpstr">
-      <vt:lpstr>TOTAL</vt:lpstr>
-      <vt:lpstr>COREOGRAFIA</vt:lpstr>
-      <vt:lpstr>MARCAÇÃO</vt:lpstr>
-      <vt:lpstr>ANIMAÇÃO</vt:lpstr>
-      <vt:lpstr>FIGURINO</vt:lpstr>
-      <vt:lpstr>CASAL DE NOIVOS</vt:lpstr>
-      <vt:lpstr>TRILHA SONORA</vt:lpstr>
-    </vt:vector>
-  </TitlesOfParts>
-  <LinksUpToDate>false</LinksUpToDate>
-  <SharedDoc>false</SharedDoc>
-  <HyperlinksChanged>false</HyperlinksChanged>
-  <AppVersion>16.0300</AppVersion>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tiago\Documents\GitHub\site-linq-dfe-beta\dashboard\assets\notas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39041062-09E9-4442-9D38-B83434B06CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="TOTAL" sheetId="8" r:id="rId1"/>
+    <sheet name="COREOGRAFIA" sheetId="16" r:id="rId2"/>
+    <sheet name="MARCAÇÃO" sheetId="17" r:id="rId3"/>
+    <sheet name="ANIMAÇÃO" sheetId="18" r:id="rId4"/>
+    <sheet name="FIGURINO" sheetId="19" r:id="rId5"/>
+    <sheet name="CASAL DE NOIVOS" sheetId="20" r:id="rId6"/>
+    <sheet name="TRILHA SONORA" sheetId="21" r:id="rId7"/>
+    <sheet name="TEMÁTICA" sheetId="22" r:id="rId8"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <dc:creator>Acer</dc:creator>
-  <cp:lastModifiedBy>Tiago</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-12T22:02:07Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-15T11:10:07Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="2" name="Created">
-    <vt:filetime>2015-07-07T00:00:00Z</vt:filetime>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="3" name="Creator">
-    <vt:lpwstr>Calc</vt:lpwstr>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="4" name="Producer">
-    <vt:lpwstr>LibreOffice 25.2.3.2 (AARCH64) / LibreOffice Community</vt:lpwstr>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="5" name="LastSaved">
-    <vt:filetime>2015-07-07T00:00:00Z</vt:filetime>
-  </property>
-</Properties>
-</file>
-
-<file path=xl\calcChain.xml><?xml version="1.0" encoding="utf-8"?>
-<calcChain xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <c r="F16" i="21" l="1"/>
-  <c r="G16" i="21" s="1"/>
-  <c r="E16" i="21"/>
-  <c r="E15" i="21"/>
-  <c r="F15" i="21" s="1"/>
-  <c r="G15" i="21" s="1"/>
-  <c r="E14" i="21"/>
-  <c r="F14" i="21" s="1"/>
-  <c r="G14" i="21" s="1"/>
-  <c r="E13" i="21"/>
-  <c r="F13" i="21" s="1"/>
-  <c r="G13" i="21" s="1"/>
-  <c r="F12" i="21"/>
-  <c r="G12" i="21" s="1"/>
-  <c r="E12" i="21"/>
-  <c r="E11" i="21"/>
-  <c r="F11" i="21" s="1"/>
-  <c r="G11" i="21" s="1"/>
-  <c r="F10" i="21"/>
-  <c r="G10" i="21" s="1"/>
-  <c r="E10" i="21"/>
-  <c r="E9" i="21"/>
-  <c r="F9" i="21" s="1"/>
-  <c r="G9" i="21" s="1"/>
-  <c r="E8" i="21"/>
-  <c r="F8" i="21" s="1"/>
-  <c r="G8" i="21" s="1"/>
-  <c r="E7" i="21"/>
-  <c r="F7" i="21" s="1"/>
-  <c r="G7" i="21" s="1"/>
-  <c r="E6" i="21"/>
-  <c r="F6" i="21" s="1"/>
-  <c r="G6" i="21" s="1"/>
-  <c r="E5" i="21"/>
-  <c r="F5" i="21" s="1"/>
-  <c r="G5" i="21" s="1"/>
-  <c r="F4" i="21"/>
-  <c r="G4" i="21" s="1"/>
-  <c r="E4" i="21"/>
-  <c r="E3" i="21"/>
-  <c r="F3" i="21" s="1"/>
-  <c r="G3" i="21" s="1"/>
-  <c r="E2" i="21"/>
-  <c r="F2" i="21" s="1"/>
-  <c r="G2" i="21" s="1"/>
-  <c r="E16" i="20"/>
-  <c r="F16" i="20" s="1"/>
-  <c r="G16" i="20" s="1"/>
-  <c r="E15" i="20"/>
-  <c r="F15" i="20" s="1"/>
-  <c r="G15" i="20" s="1"/>
-  <c r="E14" i="20"/>
-  <c r="F14" i="20" s="1"/>
-  <c r="G14" i="20" s="1"/>
-  <c r="E13" i="20"/>
-  <c r="F13" i="20" s="1"/>
-  <c r="G13" i="20" s="1"/>
-  <c r="E12" i="20"/>
-  <c r="F12" i="20" s="1"/>
-  <c r="G12" i="20" s="1"/>
-  <c r="E11" i="20"/>
-  <c r="F11" i="20" s="1"/>
-  <c r="G11" i="20" s="1"/>
-  <c r="E10" i="20"/>
-  <c r="F10" i="20" s="1"/>
-  <c r="G10" i="20" s="1"/>
-  <c r="E9" i="20"/>
-  <c r="F9" i="20" s="1"/>
-  <c r="G9" i="20" s="1"/>
-  <c r="E8" i="20"/>
-  <c r="F8" i="20" s="1"/>
-  <c r="G8" i="20" s="1"/>
-  <c r="F7" i="20"/>
-  <c r="G7" i="20" s="1"/>
-  <c r="E7" i="20"/>
-  <c r="E6" i="20"/>
-  <c r="F6" i="20" s="1"/>
-  <c r="G6" i="20" s="1"/>
-  <c r="F5" i="20"/>
-  <c r="G5" i="20" s="1"/>
-  <c r="E5" i="20"/>
-  <c r="E4" i="20"/>
-  <c r="F4" i="20" s="1"/>
-  <c r="G4" i="20" s="1"/>
-  <c r="F3" i="20"/>
-  <c r="G3" i="20" s="1"/>
-  <c r="E3" i="20"/>
-  <c r="E2" i="20"/>
-  <c r="F2" i="20" s="1"/>
-  <c r="G2" i="20" s="1"/>
-  <c r="E16" i="19"/>
-  <c r="F16" i="19" s="1"/>
-  <c r="G16" i="19" s="1"/>
-  <c r="E15" i="19"/>
-  <c r="F15" i="19" s="1"/>
-  <c r="G15" i="19" s="1"/>
-  <c r="E14" i="19"/>
-  <c r="F14" i="19" s="1"/>
-  <c r="G14" i="19" s="1"/>
-  <c r="E13" i="19"/>
-  <c r="F13" i="19" s="1"/>
-  <c r="G13" i="19" s="1"/>
-  <c r="E12" i="19"/>
-  <c r="F12" i="19" s="1"/>
-  <c r="G12" i="19" s="1"/>
-  <c r="E11" i="19"/>
-  <c r="F11" i="19" s="1"/>
-  <c r="G11" i="19" s="1"/>
-  <c r="E10" i="19"/>
-  <c r="F10" i="19" s="1"/>
-  <c r="G10" i="19" s="1"/>
-  <c r="E9" i="19"/>
-  <c r="F9" i="19" s="1"/>
-  <c r="G9" i="19" s="1"/>
-  <c r="E8" i="19"/>
-  <c r="F8" i="19" s="1"/>
-  <c r="G8" i="19" s="1"/>
-  <c r="E7" i="19"/>
-  <c r="F7" i="19" s="1"/>
-  <c r="G7" i="19" s="1"/>
-  <c r="E6" i="19"/>
-  <c r="F6" i="19" s="1"/>
-  <c r="G6" i="19" s="1"/>
-  <c r="E5" i="19"/>
-  <c r="F5" i="19" s="1"/>
-  <c r="G5" i="19" s="1"/>
-  <c r="E4" i="19"/>
-  <c r="F4" i="19" s="1"/>
-  <c r="G4" i="19" s="1"/>
-  <c r="E3" i="19"/>
-  <c r="F3" i="19" s="1"/>
-  <c r="G3" i="19" s="1"/>
-  <c r="E2" i="19"/>
-  <c r="F2" i="19" s="1"/>
-  <c r="G2" i="19" s="1"/>
-  <c r="E16" i="18"/>
-  <c r="F16" i="18" s="1"/>
-  <c r="G16" i="18" s="1"/>
-  <c r="E15" i="18"/>
-  <c r="F15" i="18" s="1"/>
-  <c r="G15" i="18" s="1"/>
-  <c r="E14" i="18"/>
-  <c r="F14" i="18" s="1"/>
-  <c r="G14" i="18" s="1"/>
-  <c r="E13" i="18"/>
-  <c r="F13" i="18" s="1"/>
-  <c r="G13" i="18" s="1"/>
-  <c r="E12" i="18"/>
-  <c r="F12" i="18" s="1"/>
-  <c r="G12" i="18" s="1"/>
-  <c r="E11" i="18"/>
-  <c r="F11" i="18" s="1"/>
-  <c r="G11" i="18" s="1"/>
-  <c r="E10" i="18"/>
-  <c r="F10" i="18" s="1"/>
-  <c r="G10" i="18" s="1"/>
-  <c r="E9" i="18"/>
-  <c r="F9" i="18" s="1"/>
-  <c r="G9" i="18" s="1"/>
-  <c r="E8" i="18"/>
-  <c r="F8" i="18" s="1"/>
-  <c r="G8" i="18" s="1"/>
-  <c r="E7" i="18"/>
-  <c r="F7" i="18" s="1"/>
-  <c r="G7" i="18" s="1"/>
-  <c r="E6" i="18"/>
-  <c r="F6" i="18" s="1"/>
-  <c r="G6" i="18" s="1"/>
-  <c r="E5" i="18"/>
-  <c r="F5" i="18" s="1"/>
-  <c r="G5" i="18" s="1"/>
-  <c r="E4" i="18"/>
-  <c r="F4" i="18" s="1"/>
-  <c r="G4" i="18" s="1"/>
-  <c r="E3" i="18"/>
-  <c r="F3" i="18" s="1"/>
-  <c r="G3" i="18" s="1"/>
-  <c r="E2" i="18"/>
-  <c r="F2" i="18" s="1"/>
-  <c r="G2" i="18" s="1"/>
-  <c r="E16" i="17"/>
-  <c r="F16" i="17" s="1"/>
-  <c r="G16" i="17" s="1"/>
-  <c r="E15" i="17"/>
-  <c r="F15" i="17" s="1"/>
-  <c r="G15" i="17" s="1"/>
-  <c r="E14" i="17"/>
-  <c r="F14" i="17" s="1"/>
-  <c r="G14" i="17" s="1"/>
-  <c r="E13" i="17"/>
-  <c r="F13" i="17" s="1"/>
-  <c r="G13" i="17" s="1"/>
-  <c r="F12" i="17"/>
-  <c r="G12" i="17" s="1"/>
-  <c r="E12" i="17"/>
-  <c r="E11" i="17"/>
-  <c r="F11" i="17" s="1"/>
-  <c r="G11" i="17" s="1"/>
-  <c r="E10" i="17"/>
-  <c r="F10" i="17" s="1"/>
-  <c r="G10" i="17" s="1"/>
-  <c r="E9" i="17"/>
-  <c r="F9" i="17" s="1"/>
-  <c r="G9" i="17" s="1"/>
-  <c r="E8" i="17"/>
-  <c r="F8" i="17" s="1"/>
-  <c r="G8" i="17" s="1"/>
-  <c r="E7" i="17"/>
-  <c r="F7" i="17" s="1"/>
-  <c r="G7" i="17" s="1"/>
-  <c r="E6" i="17"/>
-  <c r="F6" i="17" s="1"/>
-  <c r="G6" i="17" s="1"/>
-  <c r="E5" i="17"/>
-  <c r="F5" i="17" s="1"/>
-  <c r="G5" i="17" s="1"/>
-  <c r="E4" i="17"/>
-  <c r="F4" i="17" s="1"/>
-  <c r="G4" i="17" s="1"/>
-  <c r="E3" i="17"/>
-  <c r="F3" i="17" s="1"/>
-  <c r="G3" i="17" s="1"/>
-  <c r="E2" i="17"/>
-  <c r="F2" i="17" s="1"/>
-  <c r="G2" i="17" s="1"/>
-  <c r="E16" i="16"/>
-  <c r="F16" i="16" s="1"/>
-  <c r="G16" i="16" s="1"/>
-  <c r="E15" i="16"/>
-  <c r="F15" i="16" s="1"/>
-  <c r="G15" i="16" s="1"/>
-  <c r="F14" i="16"/>
-  <c r="G14" i="16" s="1"/>
-  <c r="E14" i="16"/>
-  <c r="E13" i="16"/>
-  <c r="F13" i="16" s="1"/>
-  <c r="G13" i="16" s="1"/>
-  <c r="E12" i="16"/>
-  <c r="F12" i="16" s="1"/>
-  <c r="G12" i="16" s="1"/>
-  <c r="G11" i="16"/>
-  <c r="F11" i="16"/>
-  <c r="E11" i="16"/>
-  <c r="E10" i="16"/>
-  <c r="F10" i="16" s="1"/>
-  <c r="G10" i="16" s="1"/>
-  <c r="E9" i="16"/>
-  <c r="F9" i="16" s="1"/>
-  <c r="G9" i="16" s="1"/>
-  <c r="E8" i="16"/>
-  <c r="F8" i="16" s="1"/>
-  <c r="G8" i="16" s="1"/>
-  <c r="E7" i="16"/>
-  <c r="F7" i="16" s="1"/>
-  <c r="G7" i="16" s="1"/>
-  <c r="F6" i="16"/>
-  <c r="G6" i="16" s="1"/>
-  <c r="E6" i="16"/>
-  <c r="E5" i="16"/>
-  <c r="F5" i="16" s="1"/>
-  <c r="G5" i="16" s="1"/>
-  <c r="E4" i="16"/>
-  <c r="F4" i="16" s="1"/>
-  <c r="G4" i="16" s="1"/>
-  <c r="G3" i="16"/>
-  <c r="F3" i="16"/>
-  <c r="E3" i="16"/>
-  <c r="E2" i="16"/>
-  <c r="F2" i="16" s="1"/>
-  <c r="G2" i="16" s="1"/>
-  <c r="I4" i="8"/>
-  <c r="I5" i="8"/>
-  <c r="I6" i="8"/>
-  <c r="I7" i="8"/>
-  <c r="I8" i="8"/>
-  <c r="I9" i="8"/>
-  <c r="I10" i="8"/>
-  <c r="I11" i="8"/>
-  <c r="I12" i="8"/>
-  <c r="I13" i="8"/>
-  <c r="I14" i="8"/>
-  <c r="I15" i="8"/>
-  <c r="I16" i="8"/>
-  <c r="I17" i="8"/>
-  <c r="I3" i="8"/>
-  <c r="H4" i="8"/>
-  <c r="H5" i="8"/>
-  <c r="H6" i="8"/>
-  <c r="H7" i="8"/>
-  <c r="H8" i="8"/>
-  <c r="H9" i="8"/>
-  <c r="H10" i="8"/>
-  <c r="H11" i="8"/>
-  <c r="H12" i="8"/>
-  <c r="H13" i="8"/>
-  <c r="H14" i="8"/>
-  <c r="H15" i="8"/>
-  <c r="H16" i="8"/>
-  <c r="H17" i="8"/>
-  <c r="H3" i="8"/>
-  <c r="G4" i="8"/>
-  <c r="G5" i="8"/>
-  <c r="G6" i="8"/>
-  <c r="G7" i="8"/>
-  <c r="G8" i="8"/>
-  <c r="G9" i="8"/>
-  <c r="G10" i="8"/>
-  <c r="G11" i="8"/>
-  <c r="G12" i="8"/>
-  <c r="G13" i="8"/>
-  <c r="G14" i="8"/>
-  <c r="G15" i="8"/>
-  <c r="G16" i="8"/>
-  <c r="G17" i="8"/>
-  <c r="G3" i="8"/>
-</calcChain>
-</file>
-
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="43">
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="43">
   <si>
     <r>
       <rPr>
@@ -779,13 +438,13 @@
 </sst>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -863,8 +522,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -891,8 +555,13 @@
         <fgColor rgb="FFF9D9D2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFE8B3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -933,11 +602,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1004,14 +688,20 @@
     <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1030,7 +720,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -1349,47 +1039,10 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tiago\Documents\GitHub\fantasy-junino\assets\notas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD69540C-AA0D-4636-B718-2A6BCF0AEC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="TOTAL" sheetId="8" r:id="rId1"/>
-    <sheet name="COREOGRAFIA" sheetId="16" r:id="rId2"/>
-    <sheet name="MARCAÇÃO" sheetId="17" r:id="rId3"/>
-    <sheet name="ANIMAÇÃO" sheetId="18" r:id="rId4"/>
-    <sheet name="FIGURINO" sheetId="19" r:id="rId5"/>
-    <sheet name="CASAL DE NOIVOS" sheetId="20" r:id="rId6"/>
-    <sheet name="TRILHA SONORA" sheetId="21" r:id="rId7"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
     <col min="2" max="2" width="36.1640625" customWidth="1"/>
@@ -1398,17 +1051,17 @@
     <col min="9" max="9" width="14.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:9" ht="21" customHeight="1">
+      <c r="A1" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-    </row>
-    <row r="2" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+    </row>
+    <row r="2" spans="1:9" ht="27" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>16</v>
       </c>
@@ -1431,7 +1084,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="27" customHeight="1">
       <c r="A3" s="7">
         <v>1</v>
       </c>
@@ -1450,20 +1103,20 @@
       <c r="F3" s="9">
         <v>629.20000000000005</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="22">
         <f>F3/3</f>
         <v>209.73333333333335</v>
       </c>
-      <c r="H3" s="24">
+      <c r="H3" s="22">
         <f>G3/7</f>
         <v>29.961904761904766</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="22">
         <f>H3/3</f>
         <v>9.9873015873015891</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="27" customHeight="1">
       <c r="A4" s="10">
         <v>2</v>
       </c>
@@ -1482,20 +1135,20 @@
       <c r="F4" s="12">
         <v>629.20000000000005</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="22">
         <f t="shared" ref="G4:G17" si="0">F4/3</f>
         <v>209.73333333333335</v>
       </c>
-      <c r="H4" s="24">
+      <c r="H4" s="22">
         <f t="shared" ref="H4:H17" si="1">G4/7</f>
         <v>29.961904761904766</v>
       </c>
-      <c r="I4" s="24">
+      <c r="I4" s="22">
         <f t="shared" ref="I4:I17" si="2">H4/3</f>
         <v>9.9873015873015891</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="27" customHeight="1">
       <c r="A5" s="10">
         <v>3</v>
       </c>
@@ -1514,20 +1167,20 @@
       <c r="F5" s="12">
         <v>628.4</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="22">
         <f t="shared" si="0"/>
         <v>209.46666666666667</v>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="22">
         <f t="shared" si="1"/>
         <v>29.923809523809524</v>
       </c>
-      <c r="I5" s="24">
+      <c r="I5" s="22">
         <f t="shared" si="2"/>
         <v>9.9746031746031747</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="27" customHeight="1">
       <c r="A6" s="10">
         <v>4</v>
       </c>
@@ -1546,20 +1199,20 @@
       <c r="F6" s="12">
         <v>627.70000000000005</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="22">
         <f t="shared" si="0"/>
         <v>209.23333333333335</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="22">
         <f t="shared" si="1"/>
         <v>29.890476190476193</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="22">
         <f t="shared" si="2"/>
         <v>9.9634920634920636</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="27" customHeight="1">
       <c r="A7" s="10">
         <v>5</v>
       </c>
@@ -1578,20 +1231,20 @@
       <c r="F7" s="12">
         <v>627.4</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="22">
         <f t="shared" si="0"/>
         <v>209.13333333333333</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="22">
         <f t="shared" si="1"/>
         <v>29.876190476190477</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="22">
         <f t="shared" si="2"/>
         <v>9.9587301587301589</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="27" customHeight="1">
       <c r="A8" s="13">
         <v>6</v>
       </c>
@@ -1610,20 +1263,20 @@
       <c r="F8" s="15">
         <v>626.70000000000005</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="22">
         <f t="shared" si="0"/>
         <v>208.9</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="22">
         <f t="shared" si="1"/>
         <v>29.842857142857145</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="22">
         <f t="shared" si="2"/>
         <v>9.9476190476190478</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="27" customHeight="1">
       <c r="A9" s="13">
         <v>7</v>
       </c>
@@ -1642,20 +1295,20 @@
       <c r="F9" s="15">
         <v>626</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="22">
         <f t="shared" si="0"/>
         <v>208.66666666666666</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="22">
         <f t="shared" si="1"/>
         <v>29.809523809523807</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="22">
         <f t="shared" si="2"/>
         <v>9.936507936507935</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="27" customHeight="1">
       <c r="A10" s="13">
         <v>8</v>
       </c>
@@ -1674,20 +1327,20 @@
       <c r="F10" s="15">
         <v>625.79999999999995</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="22">
         <f t="shared" si="0"/>
         <v>208.6</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="22">
         <f t="shared" si="1"/>
         <v>29.8</v>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="22">
         <f t="shared" si="2"/>
         <v>9.9333333333333336</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="27" customHeight="1">
       <c r="A11" s="13">
         <v>9</v>
       </c>
@@ -1706,20 +1359,20 @@
       <c r="F11" s="15">
         <v>625.6</v>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="22">
         <f t="shared" si="0"/>
         <v>208.53333333333333</v>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="22">
         <f t="shared" si="1"/>
         <v>29.790476190476191</v>
       </c>
-      <c r="I11" s="24">
+      <c r="I11" s="22">
         <f t="shared" si="2"/>
         <v>9.9301587301587304</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="27" customHeight="1">
       <c r="A12" s="13">
         <v>10</v>
       </c>
@@ -1738,20 +1391,20 @@
       <c r="F12" s="15">
         <v>625.20000000000005</v>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="22">
         <f t="shared" si="0"/>
         <v>208.4</v>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="22">
         <f t="shared" si="1"/>
         <v>29.771428571428572</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="22">
         <f t="shared" si="2"/>
         <v>9.9238095238095241</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="27" customHeight="1">
       <c r="A13" s="13">
         <v>11</v>
       </c>
@@ -1770,20 +1423,20 @@
       <c r="F13" s="15">
         <v>623.70000000000005</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="22">
         <f t="shared" si="0"/>
         <v>207.9</v>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="22">
         <f t="shared" si="1"/>
         <v>29.7</v>
       </c>
-      <c r="I13" s="24">
+      <c r="I13" s="22">
         <f t="shared" si="2"/>
         <v>9.9</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="27" customHeight="1">
       <c r="A14" s="13">
         <v>12</v>
       </c>
@@ -1802,20 +1455,20 @@
       <c r="F14" s="15">
         <v>622.29999999999995</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="22">
         <f t="shared" si="0"/>
         <v>207.43333333333331</v>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="22">
         <f t="shared" si="1"/>
         <v>29.633333333333329</v>
       </c>
-      <c r="I14" s="24">
+      <c r="I14" s="22">
         <f t="shared" si="2"/>
         <v>9.8777777777777764</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="27" customHeight="1">
       <c r="A15" s="16">
         <v>13</v>
       </c>
@@ -1834,20 +1487,20 @@
       <c r="F15" s="18">
         <v>622.29999999999995</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="22">
         <f t="shared" si="0"/>
         <v>207.43333333333331</v>
       </c>
-      <c r="H15" s="24">
+      <c r="H15" s="22">
         <f t="shared" si="1"/>
         <v>29.633333333333329</v>
       </c>
-      <c r="I15" s="24">
+      <c r="I15" s="22">
         <f t="shared" si="2"/>
         <v>9.8777777777777764</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="27" customHeight="1">
       <c r="A16" s="16">
         <v>14</v>
       </c>
@@ -1866,20 +1519,20 @@
       <c r="F16" s="18">
         <v>621.9</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="22">
         <f t="shared" si="0"/>
         <v>207.29999999999998</v>
       </c>
-      <c r="H16" s="24">
+      <c r="H16" s="22">
         <f t="shared" si="1"/>
         <v>29.61428571428571</v>
       </c>
-      <c r="I16" s="24">
+      <c r="I16" s="22">
         <f t="shared" si="2"/>
         <v>9.8714285714285701</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="27" customHeight="1">
       <c r="A17" s="16">
         <v>15</v>
       </c>
@@ -1898,26 +1551,26 @@
       <c r="F17" s="18">
         <v>620.5</v>
       </c>
-      <c r="G17" s="24">
+      <c r="G17" s="22">
         <f t="shared" si="0"/>
         <v>206.83333333333334</v>
       </c>
-      <c r="H17" s="24">
+      <c r="H17" s="22">
         <f t="shared" si="1"/>
         <v>29.547619047619047</v>
       </c>
-      <c r="I17" s="24">
+      <c r="I17" s="22">
         <f t="shared" si="2"/>
         <v>9.8492063492063497</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="23"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
+    <row r="18" spans="1:9" ht="21" customHeight="1">
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1929,16 +1582,16 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD82F689-65FD-4730-B49C-CFCD4C137F95}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="20" t="s">
         <v>41</v>
       </c>
@@ -1959,7 +1612,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="22.5">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1972,20 +1625,20 @@
       <c r="D2" s="2">
         <v>29.2</v>
       </c>
-      <c r="E2" s="24">
+      <c r="E2" s="22">
         <f t="shared" ref="E2:E16" si="0">SUM(B2:D2)</f>
         <v>88.6</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="22">
         <f t="shared" ref="F2:G16" si="1">E2/3</f>
         <v>29.533333333333331</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="22">
         <f t="shared" si="1"/>
         <v>9.8444444444444432</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="33.75">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1998,20 +1651,20 @@
       <c r="D3" s="2">
         <v>29</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="22">
         <f t="shared" si="0"/>
         <v>88.3</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="22">
         <f t="shared" si="1"/>
         <v>29.433333333333334</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="22">
         <f t="shared" si="1"/>
         <v>9.8111111111111118</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="22.5">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2024,20 +1677,20 @@
       <c r="D4" s="2">
         <v>29.8</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="22">
         <f t="shared" si="0"/>
         <v>89.8</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="22">
         <f t="shared" si="1"/>
         <v>29.933333333333334</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="22">
         <f t="shared" si="1"/>
         <v>9.9777777777777779</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -2050,20 +1703,20 @@
       <c r="D5" s="2">
         <v>29.5</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="22">
         <f t="shared" si="0"/>
         <v>88.6</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="22">
         <f t="shared" si="1"/>
         <v>29.533333333333331</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="22">
         <f t="shared" si="1"/>
         <v>9.8444444444444432</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="22.5">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -2076,20 +1729,20 @@
       <c r="D6" s="2">
         <v>29.1</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="22">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="22">
         <f t="shared" si="1"/>
         <v>29.333333333333332</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="22">
         <f t="shared" si="1"/>
         <v>9.7777777777777768</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="22.5">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -2102,20 +1755,20 @@
       <c r="D7" s="2">
         <v>29</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="22">
         <f t="shared" si="0"/>
         <v>88.4</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="22">
         <f t="shared" si="1"/>
         <v>29.466666666666669</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="22">
         <f t="shared" si="1"/>
         <v>9.8222222222222229</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="22.5">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -2128,20 +1781,20 @@
       <c r="D8" s="2">
         <v>29.1</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="22">
         <f t="shared" si="0"/>
         <v>87.9</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="22">
         <f t="shared" si="1"/>
         <v>29.3</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="22">
         <f t="shared" si="1"/>
         <v>9.7666666666666675</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="22.5">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -2154,20 +1807,20 @@
       <c r="D9" s="2">
         <v>29.7</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="22">
         <f t="shared" si="0"/>
         <v>89.5</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="22">
         <f t="shared" si="1"/>
         <v>29.833333333333332</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="22">
         <f t="shared" si="1"/>
         <v>9.9444444444444446</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -2180,20 +1833,20 @@
       <c r="D10" s="2">
         <v>29.1</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="22">
         <f t="shared" si="0"/>
         <v>88.6</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="22">
         <f t="shared" si="1"/>
         <v>29.533333333333331</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="22">
         <f t="shared" si="1"/>
         <v>9.8444444444444432</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="22.5">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -2206,20 +1859,20 @@
       <c r="D11" s="2">
         <v>29.8</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="22">
         <f t="shared" si="0"/>
         <v>88.8</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="22">
         <f t="shared" si="1"/>
         <v>29.599999999999998</v>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="22">
         <f t="shared" si="1"/>
         <v>9.8666666666666654</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="22.5">
       <c r="A12" s="1" t="s">
         <v>2</v>
       </c>
@@ -2232,20 +1885,20 @@
       <c r="D12" s="2">
         <v>29.5</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="22">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="22">
         <f t="shared" si="1"/>
         <v>29.666666666666668</v>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="22">
         <f t="shared" si="1"/>
         <v>9.8888888888888893</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>4</v>
       </c>
@@ -2258,20 +1911,20 @@
       <c r="D13" s="2">
         <v>29.7</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="22">
         <f t="shared" si="0"/>
         <v>89.5</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="22">
         <f t="shared" si="1"/>
         <v>29.833333333333332</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="22">
         <f t="shared" si="1"/>
         <v>9.9444444444444446</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="22.5">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -2284,20 +1937,20 @@
       <c r="D14" s="2">
         <v>29.1</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="22">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="22">
         <f t="shared" si="1"/>
         <v>29.333333333333332</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="22">
         <f t="shared" si="1"/>
         <v>9.7777777777777768</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="22.5">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -2310,20 +1963,20 @@
       <c r="D15" s="2">
         <v>29.6</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="22">
         <f t="shared" si="0"/>
         <v>88.800000000000011</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="22">
         <f t="shared" si="1"/>
         <v>29.600000000000005</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="22">
         <f t="shared" si="1"/>
         <v>9.8666666666666689</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
@@ -2336,15 +1989,15 @@
       <c r="D16" s="2">
         <v>29.3</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="22">
         <f t="shared" si="0"/>
         <v>88.6</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="22">
         <f t="shared" si="1"/>
         <v>29.533333333333331</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="22">
         <f t="shared" si="1"/>
         <v>9.8444444444444432</v>
       </c>
@@ -2355,16 +2008,16 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39BA73F9-63C3-495D-B656-318CA6A7059B}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="20" t="s">
         <v>41</v>
       </c>
@@ -2385,7 +2038,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="22.5">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2398,20 +2051,20 @@
       <c r="D2" s="2">
         <v>29.4</v>
       </c>
-      <c r="E2" s="24">
+      <c r="E2" s="22">
         <f t="shared" ref="E2:E16" si="0">SUM(B2:D2)</f>
         <v>89.1</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="22">
         <f t="shared" ref="F2:G16" si="1">E2/3</f>
         <v>29.7</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="22">
         <f t="shared" si="1"/>
         <v>9.9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="33.75">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -2424,20 +2077,20 @@
       <c r="D3" s="2">
         <v>29.5</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="22">
         <f t="shared" si="0"/>
         <v>88.7</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="22">
         <f t="shared" si="1"/>
         <v>29.566666666666666</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="22">
         <f t="shared" si="1"/>
         <v>9.8555555555555561</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="22.5">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2450,20 +2103,20 @@
       <c r="D4" s="2">
         <v>30</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="22">
         <f t="shared" si="0"/>
         <v>89.9</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="22">
         <f t="shared" si="1"/>
         <v>29.966666666666669</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="22">
         <f t="shared" si="1"/>
         <v>9.9888888888888889</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -2476,20 +2129,20 @@
       <c r="D5" s="2">
         <v>29.7</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="22">
         <f t="shared" si="0"/>
         <v>89.6</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="22">
         <f t="shared" si="1"/>
         <v>29.866666666666664</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="22">
         <f t="shared" si="1"/>
         <v>9.9555555555555539</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="22.5">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -2502,20 +2155,20 @@
       <c r="D6" s="2">
         <v>29.5</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="22">
         <f t="shared" si="0"/>
         <v>88.9</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="22">
         <f t="shared" si="1"/>
         <v>29.633333333333336</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="22">
         <f t="shared" si="1"/>
         <v>9.8777777777777782</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="22.5">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -2528,20 +2181,20 @@
       <c r="D7" s="2">
         <v>29.5</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="22">
         <f t="shared" si="0"/>
         <v>88.8</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="22">
         <f t="shared" si="1"/>
         <v>29.599999999999998</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="22">
         <f t="shared" si="1"/>
         <v>9.8666666666666654</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="22.5">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -2554,20 +2207,20 @@
       <c r="D8" s="2">
         <v>29.4</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="22">
         <f t="shared" si="0"/>
         <v>88.5</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="22">
         <f t="shared" si="1"/>
         <v>29.5</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="22">
         <f t="shared" si="1"/>
         <v>9.8333333333333339</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="22.5">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -2580,20 +2233,20 @@
       <c r="D9" s="2">
         <v>30</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="22">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="F9" s="24">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="G9" s="24">
+      <c r="F9" s="22">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G9" s="22">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -2606,20 +2259,20 @@
       <c r="D10" s="2">
         <v>29.5</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="22">
         <f t="shared" si="0"/>
         <v>89.2</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="22">
         <f t="shared" si="1"/>
         <v>29.733333333333334</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="22">
         <f t="shared" si="1"/>
         <v>9.9111111111111114</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="22.5">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -2632,20 +2285,20 @@
       <c r="D11" s="2">
         <v>29.9</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="22">
         <f t="shared" si="0"/>
         <v>89.699999999999989</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="22">
         <f t="shared" si="1"/>
         <v>29.899999999999995</v>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="22">
         <f t="shared" si="1"/>
         <v>9.966666666666665</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="22.5">
       <c r="A12" s="1" t="s">
         <v>2</v>
       </c>
@@ -2658,20 +2311,20 @@
       <c r="D12" s="2">
         <v>29.7</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="22">
         <f t="shared" si="0"/>
         <v>89.5</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="22">
         <f t="shared" si="1"/>
         <v>29.833333333333332</v>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="22">
         <f t="shared" si="1"/>
         <v>9.9444444444444446</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>4</v>
       </c>
@@ -2684,20 +2337,20 @@
       <c r="D13" s="2">
         <v>30</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="22">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="F13" s="24">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="G13" s="24">
+      <c r="F13" s="22">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G13" s="22">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="22.5">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -2710,20 +2363,20 @@
       <c r="D14" s="2">
         <v>29.7</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="22">
         <f t="shared" si="0"/>
         <v>88.4</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="22">
         <f t="shared" si="1"/>
         <v>29.466666666666669</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="22">
         <f t="shared" si="1"/>
         <v>9.8222222222222229</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="22.5">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -2736,20 +2389,20 @@
       <c r="D15" s="2">
         <v>29.7</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="22">
         <f t="shared" si="0"/>
         <v>89.4</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="22">
         <f t="shared" si="1"/>
         <v>29.8</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="22">
         <f t="shared" si="1"/>
         <v>9.9333333333333336</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
@@ -2762,15 +2415,15 @@
       <c r="D16" s="2">
         <v>29.3</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="22">
         <f t="shared" si="0"/>
         <v>89.2</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="22">
         <f t="shared" si="1"/>
         <v>29.733333333333334</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="22">
         <f t="shared" si="1"/>
         <v>9.9111111111111114</v>
       </c>
@@ -2780,16 +2433,16 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE44E741-8F5F-4AAE-A096-ED0C6A2E1E6B}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="20" t="s">
         <v>41</v>
       </c>
@@ -2810,7 +2463,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="22.5">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2823,20 +2476,20 @@
       <c r="D2" s="2">
         <v>29.7</v>
       </c>
-      <c r="E2" s="24">
+      <c r="E2" s="22">
         <f t="shared" ref="E2:E16" si="0">SUM(B2:D2)</f>
         <v>89.7</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="22">
         <f t="shared" ref="F2:G16" si="1">E2/3</f>
         <v>29.900000000000002</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="22">
         <f t="shared" si="1"/>
         <v>9.9666666666666668</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="33.75">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -2849,20 +2502,20 @@
       <c r="D3" s="2">
         <v>29.8</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="22">
         <f t="shared" si="0"/>
         <v>89.3</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="22">
         <f t="shared" si="1"/>
         <v>29.766666666666666</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="22">
         <f t="shared" si="1"/>
         <v>9.9222222222222225</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="22.5">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2875,20 +2528,20 @@
       <c r="D4" s="2">
         <v>30</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="22">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="F4" s="24">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="G4" s="24">
+      <c r="F4" s="22">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G4" s="22">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -2901,20 +2554,20 @@
       <c r="D5" s="2">
         <v>30</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="22">
         <f t="shared" si="0"/>
         <v>89.8</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="22">
         <f t="shared" si="1"/>
         <v>29.933333333333334</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="22">
         <f t="shared" si="1"/>
         <v>9.9777777777777779</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="22.5">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -2927,20 +2580,20 @@
       <c r="D6" s="2">
         <v>29.6</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="22">
         <f t="shared" si="0"/>
         <v>88.9</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="22">
         <f t="shared" si="1"/>
         <v>29.633333333333336</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="22">
         <f t="shared" si="1"/>
         <v>9.8777777777777782</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="22.5">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -2953,20 +2606,20 @@
       <c r="D7" s="2">
         <v>29.7</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="22">
         <f t="shared" si="0"/>
         <v>89.4</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="22">
         <f t="shared" si="1"/>
         <v>29.8</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="22">
         <f t="shared" si="1"/>
         <v>9.9333333333333336</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="22.5">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -2979,20 +2632,20 @@
       <c r="D8" s="2">
         <v>29.6</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="22">
         <f t="shared" si="0"/>
         <v>88.699999999999989</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="22">
         <f t="shared" si="1"/>
         <v>29.566666666666663</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="22">
         <f t="shared" si="1"/>
         <v>9.8555555555555543</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="22.5">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -3005,20 +2658,20 @@
       <c r="D9" s="2">
         <v>30</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="22">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="F9" s="24">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="G9" s="24">
+      <c r="F9" s="22">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G9" s="22">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -3031,20 +2684,20 @@
       <c r="D10" s="2">
         <v>30</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="22">
         <f t="shared" si="0"/>
         <v>89.8</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="22">
         <f t="shared" si="1"/>
         <v>29.933333333333334</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="22">
         <f t="shared" si="1"/>
         <v>9.9777777777777779</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="22.5">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -3057,20 +2710,20 @@
       <c r="D11" s="2">
         <v>30</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="22">
         <f t="shared" si="0"/>
         <v>89.6</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="22">
         <f t="shared" si="1"/>
         <v>29.866666666666664</v>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="22">
         <f t="shared" si="1"/>
         <v>9.9555555555555539</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="22.5">
       <c r="A12" s="1" t="s">
         <v>2</v>
       </c>
@@ -3083,20 +2736,20 @@
       <c r="D12" s="2">
         <v>29.9</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="22">
         <f t="shared" si="0"/>
         <v>89.9</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="22">
         <f t="shared" si="1"/>
         <v>29.966666666666669</v>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="22">
         <f t="shared" si="1"/>
         <v>9.9888888888888889</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>4</v>
       </c>
@@ -3109,20 +2762,20 @@
       <c r="D13" s="2">
         <v>30</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="22">
         <f t="shared" si="0"/>
         <v>89.8</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="22">
         <f t="shared" si="1"/>
         <v>29.933333333333334</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="22">
         <f t="shared" si="1"/>
         <v>9.9777777777777779</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="22.5">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -3135,20 +2788,20 @@
       <c r="D14" s="2">
         <v>29.4</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="22">
         <f t="shared" si="0"/>
         <v>88.5</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="22">
         <f t="shared" si="1"/>
         <v>29.5</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="22">
         <f t="shared" si="1"/>
         <v>9.8333333333333339</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="22.5">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -3161,20 +2814,20 @@
       <c r="D15" s="2">
         <v>29.9</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="22">
         <f t="shared" si="0"/>
         <v>89.699999999999989</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="22">
         <f t="shared" si="1"/>
         <v>29.899999999999995</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="22">
         <f t="shared" si="1"/>
         <v>9.966666666666665</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
@@ -3187,15 +2840,15 @@
       <c r="D16" s="2">
         <v>30</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="22">
         <f t="shared" si="0"/>
         <v>89.8</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="22">
         <f t="shared" si="1"/>
         <v>29.933333333333334</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="22">
         <f t="shared" si="1"/>
         <v>9.9777777777777779</v>
       </c>
@@ -3205,16 +2858,16 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6264AB1-7BAD-456A-9FD2-61DBA485FCBC}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="20" t="s">
         <v>41</v>
       </c>
@@ -3235,7 +2888,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="22.5">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3248,20 +2901,20 @@
       <c r="D2" s="2">
         <v>29.9</v>
       </c>
-      <c r="E2" s="24">
+      <c r="E2" s="22">
         <f t="shared" ref="E2:E16" si="0">SUM(B2:D2)</f>
         <v>89.8</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="22">
         <f t="shared" ref="F2:G16" si="1">E2/3</f>
         <v>29.933333333333334</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="22">
         <f t="shared" si="1"/>
         <v>9.9777777777777779</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="33.75">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -3274,20 +2927,20 @@
       <c r="D3" s="2">
         <v>29.9</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="22">
         <f t="shared" si="0"/>
         <v>89.199999999999989</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="22">
         <f t="shared" si="1"/>
         <v>29.733333333333331</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="22">
         <f t="shared" si="1"/>
         <v>9.9111111111111097</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="22.5">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -3300,20 +2953,20 @@
       <c r="D4" s="2">
         <v>30</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="22">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="F4" s="24">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="G4" s="24">
+      <c r="F4" s="22">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G4" s="22">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -3326,20 +2979,20 @@
       <c r="D5" s="2">
         <v>30</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="22">
         <f t="shared" si="0"/>
         <v>89.9</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="22">
         <f t="shared" si="1"/>
         <v>29.966666666666669</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="22">
         <f t="shared" si="1"/>
         <v>9.9888888888888889</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="22.5">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -3352,20 +3005,20 @@
       <c r="D6" s="2">
         <v>29.7</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="22">
         <f t="shared" si="0"/>
         <v>89.5</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="22">
         <f t="shared" si="1"/>
         <v>29.833333333333332</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="22">
         <f t="shared" si="1"/>
         <v>9.9444444444444446</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="22.5">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -3378,20 +3031,20 @@
       <c r="D7" s="2">
         <v>30</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="22">
         <f t="shared" si="0"/>
         <v>89.9</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="22">
         <f t="shared" si="1"/>
         <v>29.966666666666669</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="22">
         <f t="shared" si="1"/>
         <v>9.9888888888888889</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="22.5">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -3404,20 +3057,20 @@
       <c r="D8" s="2">
         <v>30</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="22">
         <f t="shared" si="0"/>
         <v>89.5</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="22">
         <f t="shared" si="1"/>
         <v>29.833333333333332</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="22">
         <f t="shared" si="1"/>
         <v>9.9444444444444446</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="22.5">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -3430,20 +3083,20 @@
       <c r="D9" s="2">
         <v>29.9</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="22">
         <f t="shared" si="0"/>
         <v>89.9</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="22">
         <f t="shared" si="1"/>
         <v>29.966666666666669</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="22">
         <f t="shared" si="1"/>
         <v>9.9888888888888889</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -3456,20 +3109,20 @@
       <c r="D10" s="2">
         <v>29.8</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="22">
         <f t="shared" si="0"/>
         <v>89.7</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="22">
         <f t="shared" si="1"/>
         <v>29.900000000000002</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="22">
         <f t="shared" si="1"/>
         <v>9.9666666666666668</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="22.5">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -3482,20 +3135,20 @@
       <c r="D11" s="2">
         <v>30</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="22">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="F11" s="24">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="G11" s="24">
+      <c r="F11" s="22">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G11" s="22">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="22.5">
       <c r="A12" s="1" t="s">
         <v>2</v>
       </c>
@@ -3508,20 +3161,20 @@
       <c r="D12" s="2">
         <v>30</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="22">
         <f t="shared" si="0"/>
         <v>89.9</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="22">
         <f t="shared" si="1"/>
         <v>29.966666666666669</v>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="22">
         <f t="shared" si="1"/>
         <v>9.9888888888888889</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>4</v>
       </c>
@@ -3534,20 +3187,20 @@
       <c r="D13" s="2">
         <v>30</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="22">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="F13" s="24">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="G13" s="24">
+      <c r="F13" s="22">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G13" s="22">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="22.5">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -3560,20 +3213,20 @@
       <c r="D14" s="2">
         <v>29.6</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="22">
         <f t="shared" si="0"/>
         <v>88.9</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="22">
         <f t="shared" si="1"/>
         <v>29.633333333333336</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="22">
         <f t="shared" si="1"/>
         <v>9.8777777777777782</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="22.5">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -3586,20 +3239,20 @@
       <c r="D15" s="2">
         <v>30</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="22">
         <f t="shared" si="0"/>
         <v>89.9</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="22">
         <f t="shared" si="1"/>
         <v>29.966666666666669</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="22">
         <f t="shared" si="1"/>
         <v>9.9888888888888889</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
@@ -3612,15 +3265,15 @@
       <c r="D16" s="2">
         <v>29.8</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="22">
         <f t="shared" si="0"/>
         <v>89.8</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="22">
         <f t="shared" si="1"/>
         <v>29.933333333333334</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="22">
         <f t="shared" si="1"/>
         <v>9.9777777777777779</v>
       </c>
@@ -3630,16 +3283,16 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00D3258B-34BA-4515-84FD-23FAFCFF517B}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="20" t="s">
         <v>41</v>
       </c>
@@ -3660,7 +3313,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="22.5">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3673,20 +3326,20 @@
       <c r="D2" s="2">
         <v>29.5</v>
       </c>
-      <c r="E2" s="24">
+      <c r="E2" s="22">
         <f t="shared" ref="E2:E16" si="0">SUM(B2:D2)</f>
         <v>89.2</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="22">
         <f t="shared" ref="F2:G16" si="1">E2/3</f>
         <v>29.733333333333334</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="22">
         <f t="shared" si="1"/>
         <v>9.9111111111111114</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="33.75">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -3699,20 +3352,20 @@
       <c r="D3" s="2">
         <v>29.3</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="22">
         <f t="shared" si="0"/>
         <v>88.2</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="22">
         <f t="shared" si="1"/>
         <v>29.400000000000002</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="22">
         <f t="shared" si="1"/>
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="22.5">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -3725,20 +3378,20 @@
       <c r="D4" s="2">
         <v>29.9</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="22">
         <f t="shared" si="0"/>
         <v>89.8</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="22">
         <f t="shared" si="1"/>
         <v>29.933333333333334</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="22">
         <f t="shared" si="1"/>
         <v>9.9777777777777779</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -3751,20 +3404,20 @@
       <c r="D5" s="2">
         <v>30</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="22">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="F5" s="24">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="G5" s="24">
+      <c r="F5" s="22">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G5" s="22">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="22.5">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -3777,20 +3430,20 @@
       <c r="D6" s="2">
         <v>29.2</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="22">
         <f t="shared" si="0"/>
         <v>88.4</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="22">
         <f t="shared" si="1"/>
         <v>29.466666666666669</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="22">
         <f t="shared" si="1"/>
         <v>9.8222222222222229</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="22.5">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -3803,20 +3456,20 @@
       <c r="D7" s="2">
         <v>29.6</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="22">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="22">
         <f t="shared" si="1"/>
         <v>29.666666666666668</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="22">
         <f t="shared" si="1"/>
         <v>9.8888888888888893</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="22.5">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -3829,20 +3482,20 @@
       <c r="D8" s="2">
         <v>29.6</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="22">
         <f t="shared" si="0"/>
         <v>89.1</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="22">
         <f t="shared" si="1"/>
         <v>29.7</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="22">
         <f t="shared" si="1"/>
         <v>9.9</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="22.5">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -3855,20 +3508,20 @@
       <c r="D9" s="2">
         <v>30</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="22">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="F9" s="24">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="G9" s="24">
+      <c r="F9" s="22">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G9" s="22">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -3881,20 +3534,20 @@
       <c r="D10" s="2">
         <v>29.4</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="22">
         <f t="shared" si="0"/>
         <v>89.199999999999989</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="22">
         <f t="shared" si="1"/>
         <v>29.733333333333331</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="22">
         <f t="shared" si="1"/>
         <v>9.9111111111111097</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="22.5">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -3907,20 +3560,20 @@
       <c r="D11" s="2">
         <v>30</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="22">
         <f t="shared" si="0"/>
         <v>89.4</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="22">
         <f t="shared" si="1"/>
         <v>29.8</v>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="22">
         <f t="shared" si="1"/>
         <v>9.9333333333333336</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="22.5">
       <c r="A12" s="1" t="s">
         <v>2</v>
       </c>
@@ -3933,20 +3586,20 @@
       <c r="D12" s="2">
         <v>29.8</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="22">
         <f t="shared" si="0"/>
         <v>89.4</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="22">
         <f t="shared" si="1"/>
         <v>29.8</v>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="22">
         <f t="shared" si="1"/>
         <v>9.9333333333333336</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>4</v>
       </c>
@@ -3959,20 +3612,20 @@
       <c r="D13" s="2">
         <v>29.9</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="22">
         <f t="shared" si="0"/>
         <v>89.3</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="22">
         <f t="shared" si="1"/>
         <v>29.766666666666666</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="22">
         <f t="shared" si="1"/>
         <v>9.9222222222222225</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="22.5">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -3985,20 +3638,20 @@
       <c r="D14" s="2">
         <v>29.1</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="22">
         <f t="shared" si="0"/>
         <v>88.300000000000011</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="22">
         <f t="shared" si="1"/>
         <v>29.433333333333337</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="22">
         <f t="shared" si="1"/>
         <v>9.8111111111111118</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="22.5">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -4011,20 +3664,20 @@
       <c r="D15" s="2">
         <v>29.4</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="22">
         <f t="shared" si="0"/>
         <v>88.699999999999989</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="22">
         <f t="shared" si="1"/>
         <v>29.566666666666663</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="22">
         <f t="shared" si="1"/>
         <v>9.8555555555555543</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
@@ -4037,15 +3690,15 @@
       <c r="D16" s="2">
         <v>29.6</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="22">
         <f t="shared" si="0"/>
         <v>89.4</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="22">
         <f t="shared" si="1"/>
         <v>29.8</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="22">
         <f t="shared" si="1"/>
         <v>9.9333333333333336</v>
       </c>
@@ -4055,16 +3708,16 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A152A9D-024B-4174-B2E0-4B3D884DBC47}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="20" t="s">
         <v>41</v>
       </c>
@@ -4085,7 +3738,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="22.5">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4098,20 +3751,20 @@
       <c r="D2" s="2">
         <v>30</v>
       </c>
-      <c r="E2" s="24">
+      <c r="E2" s="22">
         <f t="shared" ref="E2:E16" si="0">SUM(B2:D2)</f>
         <v>90</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="22">
         <f t="shared" ref="F2:G16" si="1">E2/3</f>
         <v>30</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="22">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="33.75">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -4124,20 +3777,20 @@
       <c r="D3" s="2">
         <v>30</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="22">
         <f t="shared" si="0"/>
         <v>89.8</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="22">
         <f t="shared" si="1"/>
         <v>29.933333333333334</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="22">
         <f t="shared" si="1"/>
         <v>9.9777777777777779</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="22.5">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -4150,20 +3803,20 @@
       <c r="D4" s="2">
         <v>30</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="22">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="F4" s="24">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="G4" s="24">
+      <c r="F4" s="22">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G4" s="22">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -4176,20 +3829,20 @@
       <c r="D5" s="2">
         <v>30</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="22">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="F5" s="24">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="G5" s="24">
+      <c r="F5" s="22">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G5" s="22">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="22.5">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -4202,20 +3855,20 @@
       <c r="D6" s="2">
         <v>29.8</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="22">
         <f t="shared" si="0"/>
         <v>89.6</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="22">
         <f t="shared" si="1"/>
         <v>29.866666666666664</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="22">
         <f t="shared" si="1"/>
         <v>9.9555555555555539</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="22.5">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -4228,20 +3881,20 @@
       <c r="D7" s="2">
         <v>29.7</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="22">
         <f t="shared" si="0"/>
         <v>89.2</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="22">
         <f t="shared" si="1"/>
         <v>29.733333333333334</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="22">
         <f t="shared" si="1"/>
         <v>9.9111111111111114</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="22.5">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -4254,20 +3907,20 @@
       <c r="D8" s="2">
         <v>29.9</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="22">
         <f t="shared" si="0"/>
         <v>89.8</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="22">
         <f t="shared" si="1"/>
         <v>29.933333333333334</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="22">
         <f t="shared" si="1"/>
         <v>9.9777777777777779</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="22.5">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -4280,20 +3933,20 @@
       <c r="D9" s="2">
         <v>30</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="22">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="F9" s="24">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="G9" s="24">
+      <c r="F9" s="22">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G9" s="22">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -4306,20 +3959,20 @@
       <c r="D10" s="2">
         <v>29.9</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="22">
         <f t="shared" si="0"/>
         <v>89.8</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="22">
         <f t="shared" si="1"/>
         <v>29.933333333333334</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="22">
         <f t="shared" si="1"/>
         <v>9.9777777777777779</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="22.5">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -4332,20 +3985,20 @@
       <c r="D11" s="2">
         <v>29.9</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="22">
         <f t="shared" si="0"/>
         <v>89.6</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="22">
         <f t="shared" si="1"/>
         <v>29.866666666666664</v>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="22">
         <f t="shared" si="1"/>
         <v>9.9555555555555539</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="22.5">
       <c r="A12" s="1" t="s">
         <v>2</v>
       </c>
@@ -4358,20 +4011,20 @@
       <c r="D12" s="2">
         <v>30</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="22">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="F12" s="24">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="G12" s="24">
+      <c r="F12" s="22">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G12" s="22">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>4</v>
       </c>
@@ -4384,20 +4037,20 @@
       <c r="D13" s="2">
         <v>30</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="22">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="F13" s="24">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="G13" s="24">
+      <c r="F13" s="22">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G13" s="22">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="22.5">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -4410,20 +4063,20 @@
       <c r="D14" s="2">
         <v>29.9</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="22">
         <f t="shared" si="0"/>
         <v>89.8</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="22">
         <f t="shared" si="1"/>
         <v>29.933333333333334</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="22">
         <f t="shared" si="1"/>
         <v>9.9777777777777779</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="22.5">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -4436,20 +4089,20 @@
       <c r="D15" s="2">
         <v>30</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="22">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="F15" s="24">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="G15" s="24">
+      <c r="F15" s="22">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G15" s="22">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
@@ -4462,17 +4115,442 @@
       <c r="D16" s="2">
         <v>30</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="22">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="F16" s="24">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="G16" s="24">
+      <c r="F16" s="22">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G16" s="22">
         <f t="shared" si="1"/>
         <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F87EB6C-506F-4660-9AC1-081587198EBA}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="19"/>
+      <c r="G1" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="22.5">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="25">
+        <v>29.6</v>
+      </c>
+      <c r="C2" s="25">
+        <v>30</v>
+      </c>
+      <c r="D2" s="25">
+        <v>29.6</v>
+      </c>
+      <c r="E2" s="22">
+        <f t="shared" ref="E2:E16" si="0">SUM(B2:D2)</f>
+        <v>89.2</v>
+      </c>
+      <c r="F2" s="22">
+        <f t="shared" ref="F2:G16" si="1">E2/3</f>
+        <v>29.733333333333334</v>
+      </c>
+      <c r="G2" s="22">
+        <f t="shared" si="1"/>
+        <v>9.9111111111111114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="33.75">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="25">
+        <v>29.6</v>
+      </c>
+      <c r="C3" s="25">
+        <v>29.8</v>
+      </c>
+      <c r="D3" s="25">
+        <v>29.4</v>
+      </c>
+      <c r="E3" s="22">
+        <f t="shared" si="0"/>
+        <v>88.800000000000011</v>
+      </c>
+      <c r="F3" s="22">
+        <f t="shared" si="1"/>
+        <v>29.600000000000005</v>
+      </c>
+      <c r="G3" s="22">
+        <f t="shared" si="1"/>
+        <v>9.8666666666666689</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="22.5">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="25">
+        <v>29.7</v>
+      </c>
+      <c r="C4" s="25">
+        <v>30</v>
+      </c>
+      <c r="D4" s="25">
+        <v>30</v>
+      </c>
+      <c r="E4" s="22">
+        <f t="shared" si="0"/>
+        <v>89.7</v>
+      </c>
+      <c r="F4" s="22">
+        <f t="shared" si="1"/>
+        <v>29.900000000000002</v>
+      </c>
+      <c r="G4" s="22">
+        <f t="shared" si="1"/>
+        <v>9.9666666666666668</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="25">
+        <v>29.8</v>
+      </c>
+      <c r="C5" s="25">
+        <v>29.7</v>
+      </c>
+      <c r="D5" s="25">
+        <v>30</v>
+      </c>
+      <c r="E5" s="22">
+        <f t="shared" si="0"/>
+        <v>89.5</v>
+      </c>
+      <c r="F5" s="22">
+        <f t="shared" si="1"/>
+        <v>29.833333333333332</v>
+      </c>
+      <c r="G5" s="22">
+        <f t="shared" si="1"/>
+        <v>9.9444444444444446</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="22.5">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="25">
+        <v>29.3</v>
+      </c>
+      <c r="C6" s="25">
+        <v>29.9</v>
+      </c>
+      <c r="D6" s="25">
+        <v>29.4</v>
+      </c>
+      <c r="E6" s="22">
+        <f t="shared" si="0"/>
+        <v>88.6</v>
+      </c>
+      <c r="F6" s="22">
+        <f t="shared" si="1"/>
+        <v>29.533333333333331</v>
+      </c>
+      <c r="G6" s="22">
+        <f t="shared" si="1"/>
+        <v>9.8444444444444432</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="22.5">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="25">
+        <v>29.6</v>
+      </c>
+      <c r="C7" s="25">
+        <v>29.9</v>
+      </c>
+      <c r="D7" s="25">
+        <v>29.5</v>
+      </c>
+      <c r="E7" s="22">
+        <f t="shared" si="0"/>
+        <v>89</v>
+      </c>
+      <c r="F7" s="22">
+        <f t="shared" si="1"/>
+        <v>29.666666666666668</v>
+      </c>
+      <c r="G7" s="22">
+        <f t="shared" si="1"/>
+        <v>9.8888888888888893</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="22.5">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="25">
+        <v>29.7</v>
+      </c>
+      <c r="C8" s="25">
+        <v>29.7</v>
+      </c>
+      <c r="D8" s="25">
+        <v>29.4</v>
+      </c>
+      <c r="E8" s="22">
+        <f t="shared" si="0"/>
+        <v>88.8</v>
+      </c>
+      <c r="F8" s="22">
+        <f t="shared" si="1"/>
+        <v>29.599999999999998</v>
+      </c>
+      <c r="G8" s="22">
+        <f t="shared" si="1"/>
+        <v>9.8666666666666654</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="22.5">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="25">
+        <v>30</v>
+      </c>
+      <c r="C9" s="25">
+        <v>30</v>
+      </c>
+      <c r="D9" s="25">
+        <v>29.8</v>
+      </c>
+      <c r="E9" s="22">
+        <f t="shared" si="0"/>
+        <v>89.8</v>
+      </c>
+      <c r="F9" s="22">
+        <f t="shared" si="1"/>
+        <v>29.933333333333334</v>
+      </c>
+      <c r="G9" s="22">
+        <f t="shared" si="1"/>
+        <v>9.9777777777777779</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="25">
+        <v>29.8</v>
+      </c>
+      <c r="C10" s="25">
+        <v>29.7</v>
+      </c>
+      <c r="D10" s="25">
+        <v>29.4</v>
+      </c>
+      <c r="E10" s="22">
+        <f t="shared" si="0"/>
+        <v>88.9</v>
+      </c>
+      <c r="F10" s="22">
+        <f t="shared" si="1"/>
+        <v>29.633333333333336</v>
+      </c>
+      <c r="G10" s="22">
+        <f t="shared" si="1"/>
+        <v>9.8777777777777782</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="22.5">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="25">
+        <v>29.8</v>
+      </c>
+      <c r="C11" s="25">
+        <v>30</v>
+      </c>
+      <c r="D11" s="25">
+        <v>29.8</v>
+      </c>
+      <c r="E11" s="22">
+        <f t="shared" si="0"/>
+        <v>89.6</v>
+      </c>
+      <c r="F11" s="22">
+        <f t="shared" si="1"/>
+        <v>29.866666666666664</v>
+      </c>
+      <c r="G11" s="22">
+        <f t="shared" si="1"/>
+        <v>9.9555555555555539</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="22.5">
+      <c r="A12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="26">
+        <v>30</v>
+      </c>
+      <c r="C12" s="26">
+        <v>30</v>
+      </c>
+      <c r="D12" s="26">
+        <v>30</v>
+      </c>
+      <c r="E12" s="22">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="F12" s="22">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G12" s="22">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="25">
+        <v>29.8</v>
+      </c>
+      <c r="C13" s="25">
+        <v>30</v>
+      </c>
+      <c r="D13" s="25">
+        <v>30</v>
+      </c>
+      <c r="E13" s="22">
+        <f t="shared" si="0"/>
+        <v>89.8</v>
+      </c>
+      <c r="F13" s="22">
+        <f t="shared" si="1"/>
+        <v>29.933333333333334</v>
+      </c>
+      <c r="G13" s="22">
+        <f t="shared" si="1"/>
+        <v>9.9777777777777779</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="22.5">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="25">
+        <v>29.5</v>
+      </c>
+      <c r="C14" s="25">
+        <v>29.7</v>
+      </c>
+      <c r="D14" s="25">
+        <v>29.4</v>
+      </c>
+      <c r="E14" s="22">
+        <f t="shared" si="0"/>
+        <v>88.6</v>
+      </c>
+      <c r="F14" s="22">
+        <f t="shared" si="1"/>
+        <v>29.533333333333331</v>
+      </c>
+      <c r="G14" s="22">
+        <f t="shared" si="1"/>
+        <v>9.8444444444444432</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="22.5">
+      <c r="A15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="25">
+        <v>29.9</v>
+      </c>
+      <c r="C15" s="25">
+        <v>29.9</v>
+      </c>
+      <c r="D15" s="25">
+        <v>30</v>
+      </c>
+      <c r="E15" s="22">
+        <f t="shared" si="0"/>
+        <v>89.8</v>
+      </c>
+      <c r="F15" s="22">
+        <f t="shared" si="1"/>
+        <v>29.933333333333334</v>
+      </c>
+      <c r="G15" s="22">
+        <f t="shared" si="1"/>
+        <v>9.9777777777777779</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="25">
+        <v>29.7</v>
+      </c>
+      <c r="C16" s="25">
+        <v>29.8</v>
+      </c>
+      <c r="D16" s="25">
+        <v>29.7</v>
+      </c>
+      <c r="E16" s="22">
+        <f t="shared" si="0"/>
+        <v>89.2</v>
+      </c>
+      <c r="F16" s="22">
+        <f t="shared" si="1"/>
+        <v>29.733333333333334</v>
+      </c>
+      <c r="G16" s="22">
+        <f t="shared" si="1"/>
+        <v>9.9111111111111114</v>
       </c>
     </row>
   </sheetData>
